--- a/Parcial 2/proyecto/V0.5/archivos_prueba/Ejemplo_Importacion_3_Copropietarios.xlsx
+++ b/Parcial 2/proyecto/V0.5/archivos_prueba/Ejemplo_Importacion_3_Copropietarios.xlsx
@@ -1,45 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sjean\Desktop\Universidad ESPE\Sexto Semestre Ing.Software\ADSW\JeancarloSanti_30723_G4_ADSW\Parcial 2\proyecto\V0.5\archivos_prueba\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D6A78C-09DF-423D-A24D-DD21AAD360BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Copropietarios" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>Nombre Completo</t>
+  </si>
+  <si>
+    <t>Número Casa</t>
+  </si>
+  <si>
+    <t>Cédula</t>
+  </si>
+  <si>
+    <t>Correo Electrónico</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Saldo Inicial</t>
+  </si>
+  <si>
+    <t>0410000038</t>
+  </si>
+  <si>
+    <t>0980000003</t>
+  </si>
+  <si>
+    <t>0510000045</t>
+  </si>
+  <si>
+    <t>ejemplo04@aligest.local</t>
+  </si>
+  <si>
+    <t>0980000004</t>
+  </si>
+  <si>
+    <t>0610000051</t>
+  </si>
+  <si>
+    <t>ejemplo05@aligest.local</t>
+  </si>
+  <si>
+    <t>0980000005</t>
+  </si>
+  <si>
+    <t>Uso</t>
+  </si>
+  <si>
+    <t>Archivo de ejemplo para comprobar la importación</t>
+  </si>
+  <si>
+    <t>Resultado esperado</t>
+  </si>
+  <si>
+    <t>Crea automáticamente los usuarios casa3, casa4 y casa5</t>
+  </si>
+  <si>
+    <t>Contraseñas</t>
+  </si>
+  <si>
+    <t>El sistema las genera y las muestra en el resumen de importación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casa4 </t>
+  </si>
+  <si>
+    <t>Casa5</t>
+  </si>
+  <si>
+    <t>Casa6</t>
+  </si>
+  <si>
+    <t>Mario Perez</t>
+  </si>
+  <si>
+    <t>Juan gonzales</t>
+  </si>
+  <si>
+    <t>Lucas Armijos</t>
+  </si>
+  <si>
+    <t>ejemplo06@aligest.local</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -62,17 +142,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,139 +488,147 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="2" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nombre Completo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Número Casa</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Cédula</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Correo Electrónico</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Teléfono</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Saldo Inicial</v>
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Ejemplo Copropietario 03</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Casa 3</v>
-      </c>
-      <c r="C2" t="str">
-        <v>0410000038</v>
-      </c>
-      <c r="D2" t="str">
-        <v>ejemplo03@aligest.local</v>
-      </c>
-      <c r="E2" t="str">
-        <v>0980000003</v>
+    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Ejemplo Copropietario 04</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Casa 4</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0510000045</v>
-      </c>
-      <c r="D3" t="str">
-        <v>ejemplo04@aligest.local</v>
-      </c>
-      <c r="E3" t="str">
-        <v>0980000004</v>
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Ejemplo Copropietario 05</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Casa 5</v>
-      </c>
-      <c r="C4" t="str">
-        <v>0610000051</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ejemplo05@aligest.local</v>
-      </c>
-      <c r="E4" t="str">
-        <v>0980000005</v>
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{06BA2E2E-0206-4291-9E6F-442C2D5C30DC}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{E7A1AC69-490B-49CA-8CFE-579BFCC90661}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{E4387E4E-80F8-4F6D-BD3A-91C21038A25C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError sqref="A1:F1 C2 C3 C4 E2:F2 E3:F3 E4:F4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="72.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Uso</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Archivo de ejemplo para comprobar la importación</v>
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Resultado esperado</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Crea automáticamente los usuarios casa3, casa4 y casa5</v>
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Contraseñas</v>
-      </c>
-      <c r="B3" t="str">
-        <v>El sistema las genera y las muestra en el resumen de importación</v>
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>